--- a/assets/Leaders.xlsx
+++ b/assets/Leaders.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +36,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +46,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,13 +88,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -456,17 +461,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -474,44 +480,106 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Active cost</t>
+          <t>Active Cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Active Description</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sonic the Hedgehog</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Choose one card in your hand to discard. If you do, draw two cards. You cannot use this effect if you do not have at least one card in your hand.</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Joker</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Gain and activate any 30-cost or below active ability from your benched supporters. Pay an extra 10 to copy 40-cost or above abilities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Kazuma Kiryu</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Yakuza</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>+10 attack this turn. Can be activated multiple times a turn.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/assets/Leaders.xlsx
+++ b/assets/Leaders.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaders" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,40 +17,61 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
-      <patternFill/>
+      <patternFill patternType="solid"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F3864"/>
+        <fgColor rgb="FF1F3864"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF2F7"/>
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
@@ -59,114 +80,165 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left>
+        <color rgb="FF000000"/>
+      </left>
+      <right>
+        <color rgb="FF000000"/>
+      </right>
+      <top>
+        <color rgb="FF000000"/>
+      </top>
+      <bottom>
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal>
+        <color rgb="FF000000"/>
+      </diagonal>
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -464,121 +536,121 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Active Ability</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Active Cost</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>IP</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Active Cost</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Active Description</t>
-        </is>
-      </c>
     </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Sonic the Hedgehog</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Discard 1 card from hand → Draw 2 cards. Cannot be used with an empty hand.</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Sonic</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="n">
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Joker</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="C3" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Activate any bench unit active with cost 3 or below. Pay 1 extra energy to copy cost-4+ actives.</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Choose one card in your hand to discard. If you do, draw two cards. You cannot use this effect if you do not have at least one card in your hand.</t>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Joker</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Persona 5</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>150</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Gain and activate any 30-cost or below active ability from your benched supporters. Pay an extra 10 to copy 40-cost or above abilities.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
         <is>
           <t>Kazuma Kiryu</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>+10 attack this turn. Can be activated multiple times per turn.</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
         <is>
           <t>Yakuza</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>+10 attack this turn. Can be activated multiple times a turn.</t>
         </is>
       </c>
     </row>

--- a/assets/Leaders.xlsx
+++ b/assets/Leaders.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaders" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leaders'!$A$1:$G$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -17,120 +19,124 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="FF000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="10"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="001A8EFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="0000CC44"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF2244"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00E8F0FF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="006677AA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00FF66CC"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
-      <patternFill patternType="solid"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
+        <fgColor rgb="000066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="000D2040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="000A1A2E"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
-      <left>
-        <color rgb="FF000000"/>
-      </left>
-      <right>
-        <color rgb="FF000000"/>
-      </right>
-      <top>
-        <color rgb="FF000000"/>
-      </top>
-      <bottom>
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal>
-        <color rgb="FF000000"/>
-      </diagonal>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </left>
       <right style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </right>
       <top style="thin">
-        <color rgb="FFCCCCCC"/>
+        <color rgb="001A3A5E"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="001A3A5E"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,107 +144,119 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -530,131 +548,156 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000066CC"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Base Damage</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Active Cost</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Active Ability</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Active Cost</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>IP</t>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Sonic the Hedgehog</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Sonic</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="D2" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="E2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>Discard 1 card from hand → Draw 2 cards. Cannot be used with an empty hand.</t>
         </is>
       </c>
-      <c r="E2" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
-        <is>
-          <t>Sonic</t>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>Once per turn. Requires ≥1 card in hand.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Joker</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Persona 5</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n">
         <v>150</v>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="D3" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Activate any bench unit active with cost 3 or below. Pay 1 extra energy to copy cost-4+ actives.</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>Persona 5</t>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>1 or 2</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Activate any bench unit active with cost ≤3 for 1 energy, or cost ≥4 for 2 energy. Joker copies the chosen unit's active. Usable once per turn.</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Does not exhaust the copied unit.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Kazuma Kiryu</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Yakuza</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="D4" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="E4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>+10 attack this turn. Can be activated multiple times per turn.</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Yakuza</t>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Stacks — use 3× for +30 on top of base.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>